--- a/data/gravel/Esker Japhy Ti 2025.xlsx
+++ b/data/gravel/Esker Japhy Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7150B99C-0AEA-7240-9108-0F1123853864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FDFF38-EEB0-DF4A-B985-46280AC334D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="2480" windowWidth="26100" windowHeight="15020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,18 +371,6 @@
     <t>a8:f35</t>
   </si>
   <si>
-    <t>S1/SM </t>
-  </si>
-  <si>
-    <t>S2/MD </t>
-  </si>
-  <si>
-    <t>S3/LG </t>
-  </si>
-  <si>
-    <t>S4/XL </t>
-  </si>
-  <si>
     <t>430-444</t>
   </si>
   <si>
@@ -411,6 +399,18 @@
   </si>
   <si>
     <t>https://eskercycles.com/cdn/shop/files/Japhy_HT_Ti_3_5_25_0016_2570faee-9339-4244-a5fa-6e0e346c5053.jpg?v=1741571448&amp;width=3840</t>
+  </si>
+  <si>
+    <t>S1/SM</t>
+  </si>
+  <si>
+    <t>S2/MD</t>
+  </si>
+  <si>
+    <t>S3/LG</t>
+  </si>
+  <si>
+    <t>S4/XL</t>
   </si>
 </sst>
 </file>
@@ -811,7 +811,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -835,12 +835,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="23" x14ac:dyDescent="0.35">
@@ -856,19 +856,18 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>113</v>
+      <c r="C8" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -890,7 +889,7 @@
         <v>660</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1057,16 +1056,16 @@
         <v>430</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1399,7 +1398,7 @@
         <v>90</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1423,7 +1422,7 @@
         <v>33</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C41" s="1"/>
     </row>
@@ -1539,7 +1538,7 @@
         <v>108</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1594,7 +1593,7 @@
         <v>54</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1668,7 +1667,7 @@
         <v>2750</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
